--- a/Pruebas calificadas/COLEGIO JUAN REY_501_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JUAN REY_501_Ajustado_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4610,7 +4546,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5116,7 +5044,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5369,7 +5293,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5622,7 +5542,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5875,7 +5791,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6128,7 +6040,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6381,7 +6289,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6634,7 +6538,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6887,7 +6787,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7140,7 +7036,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7393,7 +7285,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7646,7 +7534,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8405,7 +8281,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8646,11 +8522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8658,7 +8530,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8911,7 +8779,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9164,7 +9028,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9417,7 +9277,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9670,7 +9526,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9923,7 +9775,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10176,7 +10024,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10429,7 +10273,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10682,7 +10522,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10923,11 +10763,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10935,7 +10771,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11176,11 +11012,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11188,7 +11020,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11429,11 +11261,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11441,7 +11269,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11682,11 +11510,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11694,7 +11518,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11935,11 +11759,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11947,7 +11767,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12188,11 +12008,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12200,7 +12016,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12441,11 +12257,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12453,7 +12265,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12694,11 +12506,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12706,7 +12514,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12943,11 +12751,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12955,7 +12759,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13196,11 +13000,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13208,7 +13008,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13449,11 +13249,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13461,7 +13257,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13702,11 +13498,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13714,7 +13506,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
